--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-mii-vs-consent-policy.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-mii-vs-consent-policy.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:35:53+00:00</t>
+    <t>2026-09-14T13:44:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
